--- a/data_lake/industry/CFM/UDIMM.xlsx
+++ b/data_lake/industry/CFM/UDIMM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D62B928-3B2A-4AAC-908B-F4A9590F4EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E998DD38-E599-C748-9999-A2DE14ADB676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17960" yWindow="780" windowWidth="18040" windowHeight="20700" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 UDIMM 8GB 3200" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -75,37 +75,37 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -142,59 +142,59 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -472,20 +472,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,7 +508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -531,7 +531,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -554,7 +554,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -577,7 +577,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -600,7 +600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -646,7 +646,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -669,7 +669,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -692,7 +692,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -715,7 +715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -738,7 +738,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -761,7 +761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -784,7 +784,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -807,7 +807,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -830,7 +830,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -853,7 +853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -876,7 +876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -899,7 +899,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -922,7 +922,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -945,7 +945,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -968,7 +968,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -991,7 +991,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>46049</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -1702,6 +1702,167 @@
       </c>
       <c r="G53" s="11">
         <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="11">
+        <v>35</v>
+      </c>
+      <c r="F54" s="11">
+        <v>42</v>
+      </c>
+      <c r="G54" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>35</v>
+      </c>
+      <c r="F55" s="11">
+        <v>42</v>
+      </c>
+      <c r="G55" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>35</v>
+      </c>
+      <c r="F56" s="11">
+        <v>42</v>
+      </c>
+      <c r="G56" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>35</v>
+      </c>
+      <c r="F57" s="11">
+        <v>42</v>
+      </c>
+      <c r="G57" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>40</v>
+      </c>
+      <c r="F58" s="11">
+        <v>47</v>
+      </c>
+      <c r="G58" s="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>40</v>
+      </c>
+      <c r="F59" s="11">
+        <v>47</v>
+      </c>
+      <c r="G59" s="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>40</v>
+      </c>
+      <c r="F60" s="11">
+        <v>47</v>
+      </c>
+      <c r="G60" s="11">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1712,19 +1873,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192B0709-717A-492E-9744-92D2DEF39476}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="11.5" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1747,7 +1908,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1770,7 +1931,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1793,7 +1954,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1816,7 +1977,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1839,7 +2000,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1862,7 +2023,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1885,7 +2046,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1908,7 +2069,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1931,7 +2092,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1954,7 +2115,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1977,7 +2138,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2000,7 +2161,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2023,7 +2184,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2046,7 +2207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2069,7 +2230,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2092,7 +2253,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2115,7 +2276,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2138,7 +2299,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2161,7 +2322,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2184,7 +2345,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2207,7 +2368,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2230,7 +2391,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2253,7 +2414,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2276,7 +2437,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2299,7 +2460,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2322,7 +2483,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2345,7 +2506,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>46049</v>
       </c>
@@ -2368,7 +2529,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2391,7 +2552,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2414,7 +2575,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2437,7 +2598,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2460,7 +2621,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2483,7 +2644,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2506,7 +2667,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2529,7 +2690,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2552,7 +2713,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2575,7 +2736,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2598,7 +2759,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2621,7 +2782,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2644,7 +2805,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2667,7 +2828,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2690,7 +2851,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2713,7 +2874,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2736,7 +2897,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2759,7 +2920,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2782,7 +2943,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2805,7 +2966,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2828,7 +2989,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -2851,7 +3012,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -2874,7 +3035,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -2897,7 +3058,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -2920,7 +3081,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -2941,6 +3102,167 @@
       </c>
       <c r="G53" s="11">
         <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="11">
+        <v>74</v>
+      </c>
+      <c r="F54" s="11">
+        <v>85</v>
+      </c>
+      <c r="G54" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>74</v>
+      </c>
+      <c r="F55" s="11">
+        <v>85</v>
+      </c>
+      <c r="G55" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>74</v>
+      </c>
+      <c r="F56" s="11">
+        <v>85</v>
+      </c>
+      <c r="G56" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>74</v>
+      </c>
+      <c r="F57" s="11">
+        <v>85</v>
+      </c>
+      <c r="G57" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>79</v>
+      </c>
+      <c r="F58" s="11">
+        <v>90</v>
+      </c>
+      <c r="G58" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>79</v>
+      </c>
+      <c r="F59" s="11">
+        <v>90</v>
+      </c>
+      <c r="G59" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>79</v>
+      </c>
+      <c r="F60" s="11">
+        <v>90</v>
+      </c>
+      <c r="G60" s="11">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2951,19 +3273,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C33C41F-CAF1-4FD5-8D91-A49D334C85A7}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.59765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.6640625" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2986,7 +3308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3009,7 +3331,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3032,7 +3354,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3055,7 +3377,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3078,7 +3400,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3101,7 +3423,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3124,7 +3446,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3147,7 +3469,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3170,7 +3492,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3193,7 +3515,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3216,7 +3538,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3239,7 +3561,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3262,7 +3584,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3285,7 +3607,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3308,7 +3630,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3331,7 +3653,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3354,7 +3676,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3377,7 +3699,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3400,7 +3722,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3423,7 +3745,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3446,7 +3768,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3469,7 +3791,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3492,7 +3814,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3515,7 +3837,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3538,7 +3860,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3561,7 +3883,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3584,7 +3906,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>46049</v>
       </c>
@@ -3607,7 +3929,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3630,7 +3952,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3653,7 +3975,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3676,7 +3998,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3699,7 +4021,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3722,7 +4044,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3745,7 +4067,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3768,7 +4090,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3791,7 +4113,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3814,7 +4136,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3837,7 +4159,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3860,7 +4182,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3883,7 +4205,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3906,7 +4228,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3929,7 +4251,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3952,7 +4274,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3975,7 +4297,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3998,7 +4320,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -4021,7 +4343,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4044,7 +4366,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4067,7 +4389,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -4090,7 +4412,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -4113,7 +4435,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -4136,7 +4458,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -4159,7 +4481,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -4180,6 +4502,167 @@
       </c>
       <c r="G53" s="14">
         <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="14">
+        <v>155</v>
+      </c>
+      <c r="F54" s="14">
+        <v>170</v>
+      </c>
+      <c r="G54" s="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="14">
+        <v>155</v>
+      </c>
+      <c r="F55" s="14">
+        <v>170</v>
+      </c>
+      <c r="G55" s="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="14">
+        <v>155</v>
+      </c>
+      <c r="F56" s="14">
+        <v>170</v>
+      </c>
+      <c r="G56" s="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="14">
+        <v>155</v>
+      </c>
+      <c r="F57" s="14">
+        <v>170</v>
+      </c>
+      <c r="G57" s="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="14">
+        <v>175</v>
+      </c>
+      <c r="F58" s="14">
+        <v>190</v>
+      </c>
+      <c r="G58" s="14">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="14">
+        <v>175</v>
+      </c>
+      <c r="F59" s="14">
+        <v>190</v>
+      </c>
+      <c r="G59" s="14">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="14">
+        <v>175</v>
+      </c>
+      <c r="F60" s="14">
+        <v>190</v>
+      </c>
+      <c r="G60" s="14">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -4190,20 +4673,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{804C6E38-9512-4F25-B73E-A84B442434F8}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.796875" style="5"/>
+    <col min="8" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4226,7 +4709,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
         <v>46161</v>
       </c>
@@ -4249,7 +4732,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>46168</v>
       </c>
@@ -4272,7 +4755,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>46175</v>
       </c>
@@ -4295,7 +4778,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <v>46182</v>
       </c>
@@ -4318,7 +4801,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>46189</v>
       </c>
@@ -4341,7 +4824,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>46196</v>
       </c>
@@ -4364,7 +4847,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>46203</v>
       </c>
@@ -4387,7 +4870,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <v>46210</v>
       </c>
@@ -4410,7 +4893,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>46217</v>
       </c>
@@ -4433,7 +4916,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>46224</v>
       </c>
@@ -4456,7 +4939,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>46231</v>
       </c>
@@ -4479,7 +4962,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <v>46238</v>
       </c>
@@ -4500,6 +4983,167 @@
       </c>
       <c r="G13" s="16">
         <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="16">
+        <v>77</v>
+      </c>
+      <c r="F14" s="16">
+        <v>92</v>
+      </c>
+      <c r="G14" s="16">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="16">
+        <v>77</v>
+      </c>
+      <c r="F15" s="16">
+        <v>92</v>
+      </c>
+      <c r="G15" s="16">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="16">
+        <v>77</v>
+      </c>
+      <c r="F16" s="16">
+        <v>92</v>
+      </c>
+      <c r="G16" s="16">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="16">
+        <v>77</v>
+      </c>
+      <c r="F17" s="16">
+        <v>92</v>
+      </c>
+      <c r="G17" s="16">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="16">
+        <v>80</v>
+      </c>
+      <c r="F18" s="16">
+        <v>95</v>
+      </c>
+      <c r="G18" s="16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B19" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="16">
+        <v>80</v>
+      </c>
+      <c r="F19" s="16">
+        <v>95</v>
+      </c>
+      <c r="G19" s="16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B20" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="16">
+        <v>80</v>
+      </c>
+      <c r="F20" s="16">
+        <v>95</v>
+      </c>
+      <c r="G20" s="16">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -4510,20 +5154,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04103911-DA80-4A49-87A1-FE7A2CF5D7A5}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.796875" style="5"/>
+    <col min="8" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4546,7 +5190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
         <v>46161</v>
       </c>
@@ -4569,7 +5213,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>46168</v>
       </c>
@@ -4592,7 +5236,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>46175</v>
       </c>
@@ -4615,7 +5259,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <v>46182</v>
       </c>
@@ -4638,7 +5282,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>46189</v>
       </c>
@@ -4661,7 +5305,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>46196</v>
       </c>
@@ -4684,7 +5328,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>46203</v>
       </c>
@@ -4707,7 +5351,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <v>46210</v>
       </c>
@@ -4730,7 +5374,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>46217</v>
       </c>
@@ -4753,7 +5397,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>46224</v>
       </c>
@@ -4776,7 +5420,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>46231</v>
       </c>
@@ -4799,7 +5443,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <v>46238</v>
       </c>
@@ -4820,6 +5464,167 @@
       </c>
       <c r="G13" s="16">
         <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="16">
+        <v>82</v>
+      </c>
+      <c r="F14" s="16">
+        <v>97</v>
+      </c>
+      <c r="G14" s="16">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="16">
+        <v>82</v>
+      </c>
+      <c r="F15" s="16">
+        <v>97</v>
+      </c>
+      <c r="G15" s="16">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="16">
+        <v>82</v>
+      </c>
+      <c r="F16" s="16">
+        <v>97</v>
+      </c>
+      <c r="G16" s="16">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="16">
+        <v>82</v>
+      </c>
+      <c r="F17" s="16">
+        <v>97</v>
+      </c>
+      <c r="G17" s="16">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="16">
+        <v>85</v>
+      </c>
+      <c r="F18" s="16">
+        <v>100</v>
+      </c>
+      <c r="G18" s="16">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B19" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="16">
+        <v>85</v>
+      </c>
+      <c r="F19" s="16">
+        <v>100</v>
+      </c>
+      <c r="G19" s="16">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B20" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="16">
+        <v>85</v>
+      </c>
+      <c r="F20" s="16">
+        <v>100</v>
+      </c>
+      <c r="G20" s="16">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -4830,20 +5635,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A33F9B6-7347-4C68-802E-E71624384C9E}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4866,7 +5671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4889,7 +5694,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -4912,7 +5717,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -4935,7 +5740,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -4958,7 +5763,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -4981,7 +5786,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5004,7 +5809,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5027,7 +5832,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5050,7 +5855,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5073,7 +5878,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5096,7 +5901,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5119,7 +5924,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5142,7 +5947,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5165,7 +5970,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5188,7 +5993,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5211,7 +6016,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5234,7 +6039,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5257,7 +6062,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5280,7 +6085,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5303,7 +6108,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5326,7 +6131,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5349,7 +6154,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -5372,7 +6177,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -5395,7 +6200,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -5418,7 +6223,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -5441,7 +6246,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -5464,7 +6269,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>46049</v>
       </c>
@@ -5487,7 +6292,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -5510,7 +6315,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -5533,7 +6338,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -5556,7 +6361,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -5579,7 +6384,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -5602,7 +6407,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -5625,7 +6430,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -5648,7 +6453,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5671,7 +6476,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5694,7 +6499,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5717,7 +6522,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5740,7 +6545,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -5763,7 +6568,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -5786,7 +6591,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -5809,7 +6614,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -5832,7 +6637,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -5855,7 +6660,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -5878,7 +6683,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -5901,7 +6706,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -5924,7 +6729,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -5947,7 +6752,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -5970,7 +6775,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -5993,7 +6798,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -6016,7 +6821,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -6039,7 +6844,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -6060,6 +6865,167 @@
       </c>
       <c r="G53" s="11">
         <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="11">
+        <v>157</v>
+      </c>
+      <c r="F54" s="11">
+        <v>161</v>
+      </c>
+      <c r="G54" s="11">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>173</v>
+      </c>
+      <c r="F55" s="11">
+        <v>177</v>
+      </c>
+      <c r="G55" s="11">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>173</v>
+      </c>
+      <c r="F56" s="11">
+        <v>177</v>
+      </c>
+      <c r="G56" s="11">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>173</v>
+      </c>
+      <c r="F57" s="11">
+        <v>177</v>
+      </c>
+      <c r="G57" s="11">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>188</v>
+      </c>
+      <c r="F58" s="11">
+        <v>192</v>
+      </c>
+      <c r="G58" s="11">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>188</v>
+      </c>
+      <c r="F59" s="11">
+        <v>192</v>
+      </c>
+      <c r="G59" s="11">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>188</v>
+      </c>
+      <c r="F60" s="11">
+        <v>192</v>
+      </c>
+      <c r="G60" s="11">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -6070,20 +7036,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55494817-78A6-45DF-9F77-86066DAB20E2}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6106,7 +7072,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6129,7 +7095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6152,7 +7118,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6175,7 +7141,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6198,7 +7164,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -6221,7 +7187,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -6244,7 +7210,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -6267,7 +7233,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -6290,7 +7256,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -6313,7 +7279,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -6336,7 +7302,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -6359,7 +7325,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -6382,7 +7348,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -6405,7 +7371,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -6428,7 +7394,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -6451,7 +7417,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -6474,7 +7440,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -6497,7 +7463,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -6520,7 +7486,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -6543,7 +7509,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -6566,7 +7532,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -6589,7 +7555,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -6612,7 +7578,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -6635,7 +7601,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -6658,7 +7624,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -6681,7 +7647,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -6704,7 +7670,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>46049</v>
       </c>
@@ -6727,7 +7693,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -6750,7 +7716,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -6773,7 +7739,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -6796,7 +7762,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -6819,7 +7785,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -6842,7 +7808,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -6865,7 +7831,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -6888,7 +7854,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -6911,7 +7877,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -6934,7 +7900,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -6957,7 +7923,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -6980,7 +7946,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -7003,7 +7969,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -7026,7 +7992,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -7049,7 +8015,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -7072,7 +8038,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -7095,7 +8061,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -7118,7 +8084,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -7141,7 +8107,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -7164,7 +8130,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -7187,7 +8153,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -7210,7 +8176,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -7233,7 +8199,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -7256,7 +8222,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -7279,7 +8245,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -7300,6 +8266,167 @@
       </c>
       <c r="G53" s="16">
         <v>162</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="16">
+        <v>159</v>
+      </c>
+      <c r="F54" s="16">
+        <v>164</v>
+      </c>
+      <c r="G54" s="16">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="16">
+        <v>177</v>
+      </c>
+      <c r="F55" s="16">
+        <v>182</v>
+      </c>
+      <c r="G55" s="16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="16">
+        <v>177</v>
+      </c>
+      <c r="F56" s="16">
+        <v>182</v>
+      </c>
+      <c r="G56" s="16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="16">
+        <v>177</v>
+      </c>
+      <c r="F57" s="16">
+        <v>182</v>
+      </c>
+      <c r="G57" s="16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="16">
+        <v>192</v>
+      </c>
+      <c r="F58" s="16">
+        <v>197</v>
+      </c>
+      <c r="G58" s="16">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="16">
+        <v>192</v>
+      </c>
+      <c r="F59" s="16">
+        <v>197</v>
+      </c>
+      <c r="G59" s="16">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="16">
+        <v>192</v>
+      </c>
+      <c r="F60" s="16">
+        <v>197</v>
+      </c>
+      <c r="G60" s="16">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -7310,19 +8437,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B6A378-E9BB-4F97-B1F3-B76BB8A3CEFF}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7345,7 +8472,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -7368,7 +8495,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -7391,7 +8518,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -7414,7 +8541,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -7437,7 +8564,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -7460,7 +8587,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -7483,7 +8610,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -7506,7 +8633,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -7529,7 +8656,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -7552,7 +8679,7 @@
         <v>69.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -7575,7 +8702,7 @@
         <v>69.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -7598,7 +8725,7 @@
         <v>69.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -7621,7 +8748,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -7644,7 +8771,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -7667,7 +8794,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -7690,7 +8817,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -7713,7 +8840,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -7736,7 +8863,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -7759,7 +8886,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -7782,7 +8909,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -7805,7 +8932,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -7828,7 +8955,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -7851,7 +8978,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -7874,7 +9001,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -7897,7 +9024,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -7920,7 +9047,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -7943,7 +9070,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>46049</v>
       </c>
@@ -7966,7 +9093,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -7989,7 +9116,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -8012,7 +9139,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -8035,7 +9162,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -8058,7 +9185,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -8081,7 +9208,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -8104,7 +9231,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -8127,7 +9254,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -8150,7 +9277,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -8173,7 +9300,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -8196,7 +9323,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -8219,7 +9346,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -8242,7 +9369,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -8265,7 +9392,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -8288,7 +9415,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -8311,7 +9438,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -8334,7 +9461,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -8357,7 +9484,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -8380,7 +9507,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -8403,7 +9530,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -8426,7 +9553,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -8449,7 +9576,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -8472,7 +9599,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -8495,7 +9622,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -8518,7 +9645,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -8539,6 +9666,167 @@
       </c>
       <c r="G53" s="11">
         <v>261</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="11">
+        <v>258</v>
+      </c>
+      <c r="F54" s="11">
+        <v>264</v>
+      </c>
+      <c r="G54" s="11">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>277</v>
+      </c>
+      <c r="F55" s="11">
+        <v>283</v>
+      </c>
+      <c r="G55" s="11">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>277</v>
+      </c>
+      <c r="F56" s="11">
+        <v>283</v>
+      </c>
+      <c r="G56" s="11">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>277</v>
+      </c>
+      <c r="F57" s="11">
+        <v>283</v>
+      </c>
+      <c r="G57" s="11">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>307</v>
+      </c>
+      <c r="F58" s="11">
+        <v>313</v>
+      </c>
+      <c r="G58" s="11">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>307</v>
+      </c>
+      <c r="F59" s="11">
+        <v>313</v>
+      </c>
+      <c r="G59" s="11">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>307</v>
+      </c>
+      <c r="F60" s="11">
+        <v>313</v>
+      </c>
+      <c r="G60" s="11">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -8549,19 +9837,19 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D2BE078-281B-4EE8-A7DD-0530E85C5130}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8584,7 +9872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -8607,7 +9895,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -8630,7 +9918,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -8653,7 +9941,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -8676,7 +9964,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -8699,7 +9987,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -8722,7 +10010,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -8745,7 +10033,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -8768,7 +10056,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -8791,7 +10079,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -8814,7 +10102,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -8837,7 +10125,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -8860,7 +10148,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -8883,7 +10171,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -8906,7 +10194,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -8929,7 +10217,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -8952,7 +10240,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -8975,7 +10263,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -8998,7 +10286,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -9021,7 +10309,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -9044,7 +10332,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -9067,7 +10355,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -9090,7 +10378,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -9113,7 +10401,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -9136,7 +10424,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -9159,7 +10447,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -9182,7 +10470,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>46049</v>
       </c>
@@ -9205,7 +10493,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -9228,7 +10516,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -9251,7 +10539,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -9274,7 +10562,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -9297,7 +10585,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -9320,7 +10608,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -9343,7 +10631,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -9366,7 +10654,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -9389,7 +10677,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -9412,7 +10700,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -9435,7 +10723,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -9458,7 +10746,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -9481,7 +10769,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -9504,7 +10792,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -9527,7 +10815,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -9550,7 +10838,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -9573,7 +10861,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -9596,7 +10884,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -9619,7 +10907,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -9642,7 +10930,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -9665,7 +10953,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -9688,7 +10976,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -9711,7 +10999,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -9734,7 +11022,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -9757,7 +11045,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -9778,6 +11066,167 @@
       </c>
       <c r="G53" s="11">
         <v>270</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="11">
+        <v>267</v>
+      </c>
+      <c r="F54" s="11">
+        <v>273</v>
+      </c>
+      <c r="G54" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>287</v>
+      </c>
+      <c r="F55" s="11">
+        <v>293</v>
+      </c>
+      <c r="G55" s="11">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>287</v>
+      </c>
+      <c r="F56" s="11">
+        <v>293</v>
+      </c>
+      <c r="G56" s="11">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>287</v>
+      </c>
+      <c r="F57" s="11">
+        <v>293</v>
+      </c>
+      <c r="G57" s="11">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>317</v>
+      </c>
+      <c r="F58" s="11">
+        <v>323</v>
+      </c>
+      <c r="G58" s="11">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>317</v>
+      </c>
+      <c r="F59" s="11">
+        <v>323</v>
+      </c>
+      <c r="G59" s="11">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>317</v>
+      </c>
+      <c r="F60" s="11">
+        <v>323</v>
+      </c>
+      <c r="G60" s="11">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
